--- a/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613807388</v>
+        <v>10.84497632686876</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907126542899</v>
+        <v>37.78907192328044</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.151050277733766</v>
+        <v>4.871432108472673</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04229726674062</v>
+        <v>6.539421457988005</v>
       </c>
       <c r="D2" t="n">
-        <v>28.5924201384841</v>
+        <v>27.41530464109218</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.34181243199391</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34672117051515</v>
+        <v>21.49045724596268</v>
       </c>
       <c r="D3" t="n">
-        <v>76.9641112744287</v>
+        <v>77.38626278725484</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.12675293150163</v>
+        <v>28.53744226704628</v>
       </c>
       <c r="C4" t="n">
-        <v>62.03958267446869</v>
+        <v>79.52450928710439</v>
       </c>
       <c r="D4" t="n">
-        <v>87.79475194767952</v>
+        <v>83.95317318096176</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.08738521234053</v>
+        <v>37.3064127613788</v>
       </c>
       <c r="C5" t="n">
-        <v>95.00863407848509</v>
+        <v>124.5346962837079</v>
       </c>
       <c r="D5" t="n">
-        <v>62.29189183446013</v>
+        <v>59.81297888123694</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.7850069194325</v>
+        <v>35.74347041621788</v>
       </c>
       <c r="C6" t="n">
-        <v>105.1775767990735</v>
+        <v>113.5499212208904</v>
       </c>
       <c r="D6" t="n">
-        <v>44.19631814978292</v>
+        <v>43.63279496754524</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.13536767666159</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>107.4964648765045</v>
+        <v>110.3710221545391</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.69109363052752</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>80.52785544084462</v>
+        <v>82.86441497695203</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683725620301957</v>
+        <v>7.691284669437996</v>
       </c>
       <c r="C21" t="n">
-        <v>93.16517314616122</v>
+        <v>94.21823720061545</v>
       </c>
       <c r="D21" t="n">
-        <v>7.683725620301957</v>
+        <v>8.652695253117745</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.218610942877548</v>
+        <v>5.156138942704248</v>
       </c>
       <c r="C2" t="n">
-        <v>8.828857104291567</v>
+        <v>18.12404436810036</v>
       </c>
       <c r="D2" t="n">
-        <v>36.74288957914113</v>
+        <v>29.68216009019806</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.06477965294707</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85003894762427</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="D3" t="n">
-        <v>80.76347488986386</v>
+        <v>80.30205346886785</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.89251614081414</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>55.76032435810609</v>
+        <v>65.75353423963438</v>
       </c>
       <c r="D4" t="n">
-        <v>103.4546095781204</v>
+        <v>100.5319466625776</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.98354093986863</v>
+        <v>39.71169463678348</v>
       </c>
       <c r="C5" t="n">
-        <v>104.4579557318607</v>
+        <v>135.2848336452105</v>
       </c>
       <c r="D5" t="n">
-        <v>76.15907815694632</v>
+        <v>73.01748550335654</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.95609306187872</v>
+        <v>42.50574860306991</v>
       </c>
       <c r="C6" t="n">
-        <v>125.9474312301191</v>
+        <v>152.2317625159189</v>
       </c>
       <c r="D6" t="n">
-        <v>52.48815925985148</v>
+        <v>51.40136455125026</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.63359678880023</v>
+        <v>33.29695513723482</v>
       </c>
       <c r="C7" t="n">
-        <v>129.5347373414369</v>
+        <v>136.7211305365236</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36974333606933</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="C8" t="n">
-        <v>109.5679525324653</v>
+        <v>112.5721005074605</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.864500186564158</v>
+        <v>7.872104724529456</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2554399020135</v>
+        <v>102.3373614188829</v>
       </c>
       <c r="D21" t="n">
-        <v>8.847562709884677</v>
+        <v>9.840130905661821</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.857728698342223</v>
+        <v>6.428483967408114</v>
       </c>
       <c r="C2" t="n">
-        <v>7.529023143868788</v>
+        <v>17.90805987316607</v>
       </c>
       <c r="D2" t="n">
-        <v>31.97061398879738</v>
+        <v>26.57394685855266</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.66288498901162</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C3" t="n">
-        <v>31.71535958569321</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D3" t="n">
-        <v>89.4175809027995</v>
+        <v>83.3356538749905</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>27.6695772964921</v>
       </c>
       <c r="C4" t="n">
-        <v>64.24753326131977</v>
+        <v>61.61841290934681</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6475151542383</v>
+        <v>112.0949711231966</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.70159942230054</v>
+        <v>40.66889864842413</v>
       </c>
       <c r="C5" t="n">
-        <v>102.4453729381547</v>
+        <v>127.430852011236</v>
       </c>
       <c r="D5" t="n">
-        <v>90.7871189502238</v>
+        <v>87.4000893705723</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.07434475474484</v>
+        <v>46.97368240509714</v>
       </c>
       <c r="C6" t="n">
-        <v>143.5374048471092</v>
+        <v>179.60288851032</v>
       </c>
       <c r="D6" t="n">
-        <v>62.18880832551422</v>
+        <v>60.53849043467533</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.85613472249477</v>
+        <v>40.42346172236242</v>
       </c>
       <c r="C7" t="n">
-        <v>151.4532365864512</v>
+        <v>171.3954777028166</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.88287859022092</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="C8" t="n">
-        <v>136.1880415331175</v>
+        <v>141.9459918185251</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.30468594568177</v>
+        <v>13.97812381306608</v>
       </c>
       <c r="C9" t="n">
-        <v>99.95467901248047</v>
+        <v>102.8390537675576</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>59.93078860574654</v>
+        <v>61.78138302825178</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>40.69246059332603</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029117646034674</v>
+        <v>8.036514504153706</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3967279272224</v>
+        <v>110.5020744321135</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03639705754334</v>
+        <v>11.05020744321135</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.989863727788043</v>
+        <v>5.85121631731099</v>
       </c>
       <c r="C2" t="n">
-        <v>5.118832529942869</v>
+        <v>12.17661677577319</v>
       </c>
       <c r="D2" t="n">
-        <v>26.26273283630642</v>
+        <v>22.05888916672158</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.14318060056657</v>
+        <v>19.06063167795183</v>
       </c>
       <c r="C3" t="n">
-        <v>44.92477494633405</v>
+        <v>64.39283192154829</v>
       </c>
       <c r="D3" t="n">
-        <v>95.95111187456202</v>
+        <v>89.2457750545563</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.79345743367645</v>
+        <v>19.53972455762427</v>
       </c>
       <c r="C4" t="n">
-        <v>86.90136153681492</v>
+        <v>97.32850390362029</v>
       </c>
       <c r="D4" t="n">
-        <v>107.4621037068559</v>
+        <v>104.5777289517787</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.51472320112837</v>
+        <v>26.45810062945155</v>
       </c>
       <c r="C5" t="n">
-        <v>85.75566196595889</v>
+        <v>107.3050240741764</v>
       </c>
       <c r="D5" t="n">
-        <v>61.55558105627502</v>
+        <v>59.66571672559991</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.05290086950487</v>
+        <v>25.07678160957628</v>
       </c>
       <c r="C6" t="n">
-        <v>99.74360325606746</v>
+        <v>112.8656430710303</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22899356146354</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>95.75868932452963</v>
+        <v>99.77109219178635</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>75.77128781376882</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>45.70624611891449</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.529203070318036</v>
+        <v>3.496003574822891</v>
       </c>
       <c r="C2" t="n">
-        <v>2.488730430265664</v>
+        <v>5.432991795301848</v>
       </c>
       <c r="D2" t="n">
-        <v>18.53736015158827</v>
+        <v>15.24261485613598</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.76797305109504</v>
+        <v>20.07674055184727</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07017141755381</v>
+        <v>56.98063675448488</v>
       </c>
       <c r="D3" t="n">
-        <v>95.22952731194061</v>
+        <v>87.82224088339842</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.4285503873329</v>
+        <v>26.84000048640355</v>
       </c>
       <c r="C4" t="n">
-        <v>101.3742861928214</v>
+        <v>131.3283903970958</v>
       </c>
       <c r="D4" t="n">
-        <v>128.0611340373625</v>
+        <v>120.7480953884279</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>29.25608158655496</v>
       </c>
       <c r="C5" t="n">
-        <v>121.663084248786</v>
+        <v>141.3716694115407</v>
       </c>
       <c r="D5" t="n">
-        <v>78.95705911404974</v>
+        <v>76.62540831646356</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.05039759474864</v>
+        <v>29.66547037922588</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9838947638964</v>
+        <v>141.5248220534032</v>
       </c>
       <c r="D6" t="n">
-        <v>37.51454327467913</v>
+        <v>37.0315234041897</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>118.5754877189298</v>
+        <v>125.5822210841392</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>94.54721265748907</v>
+        <v>97.9686034067892</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>52.25155806312797</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.721625620350411</v>
+        <v>3.158282364561989</v>
       </c>
       <c r="C2" t="n">
-        <v>3.274128593663113</v>
+        <v>9.185231520933158</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74887787635784</v>
+        <v>19.5760492226814</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.71058971589222</v>
+        <v>15.96321767105314</v>
       </c>
       <c r="C3" t="n">
-        <v>20.7296027751714</v>
+        <v>37.88564390688441</v>
       </c>
       <c r="D3" t="n">
-        <v>89.22123136195013</v>
+        <v>80.34132337703772</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.58767563087889</v>
+        <v>32.40454647407447</v>
       </c>
       <c r="C4" t="n">
-        <v>91.72566975548375</v>
+        <v>138.0926320793563</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6699407871825</v>
+        <v>134.6339349172949</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.66385104118265</v>
+        <v>34.26299487821369</v>
       </c>
       <c r="C5" t="n">
-        <v>153.5944283294135</v>
+        <v>189.6491127678776</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2490233973053</v>
+        <v>98.17477042468106</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.08814597586652</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>155.290888362352</v>
+        <v>180.0456567249353</v>
       </c>
       <c r="D6" t="n">
-        <v>50.2340665309008</v>
+        <v>49.26802678992194</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.81786225756237</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>144.8657094909551</v>
+        <v>163.3706719683032</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>123.7542068588317</v>
+        <v>129.7625028088221</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>79.32030576462103</v>
+        <v>82.20468051969816</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.401755795215198</v>
+        <v>1.890846078379357</v>
       </c>
       <c r="C2" t="n">
-        <v>1.554106615822701</v>
+        <v>4.391357481095983</v>
       </c>
       <c r="D2" t="n">
-        <v>17.28857707178633</v>
+        <v>13.67181852934108</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.74004214701962</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="C3" t="n">
-        <v>18.63357142660446</v>
+        <v>39.42698780255191</v>
       </c>
       <c r="D3" t="n">
-        <v>90.81166264282996</v>
+        <v>80.36095833112267</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.62895009218627</v>
+        <v>35.65904011365264</v>
       </c>
       <c r="C4" t="n">
-        <v>86.27598824920969</v>
+        <v>135.9229696529709</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3268121167816</v>
+        <v>143.8996697499762</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="C5" t="n">
-        <v>180.4943154257761</v>
+        <v>232.944186525162</v>
       </c>
       <c r="D5" t="n">
-        <v>108.4340339340602</v>
+        <v>103.9916255723434</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>189.5852991671016</v>
+        <v>216.2721470116427</v>
       </c>
       <c r="D6" t="n">
-        <v>49.3887817575443</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -2716,10 +2716,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>156.5435984329709</v>
+        <v>171.0960446530214</v>
       </c>
       <c r="D7" t="n">
         <v>34.13536767666159</v>
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>96.04928664498669</v>
+        <v>98.71964040053801</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.684499134038279</v>
+        <v>2.679189484889545</v>
       </c>
       <c r="C2" t="n">
-        <v>8.665886985386596</v>
+        <v>4.857687640613218</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87213611873644</v>
+        <v>11.55026174046372</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2212373908208</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="C3" t="n">
-        <v>12.10985793188441</v>
+        <v>28.28415135935061</v>
       </c>
       <c r="D3" t="n">
-        <v>84.11123456134548</v>
+        <v>74.09740797802802</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.15298238207581</v>
+        <v>32.68532631748906</v>
       </c>
       <c r="C4" t="n">
-        <v>67.1446707365521</v>
+        <v>118.9996027271644</v>
       </c>
       <c r="D4" t="n">
-        <v>162.979936382013</v>
+        <v>149.5025038981128</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.88094045700822</v>
+        <v>43.36870483510285</v>
       </c>
       <c r="C5" t="n">
-        <v>171.8794793210103</v>
+        <v>240.3809253848316</v>
       </c>
       <c r="D5" t="n">
-        <v>135.0884841043611</v>
+        <v>125.6882498361979</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>36.26674194258143</v>
       </c>
       <c r="C6" t="n">
-        <v>234.626902090241</v>
+        <v>286.954054726596</v>
       </c>
       <c r="D6" t="n">
-        <v>65.97246397768143</v>
+        <v>64.76491430145784</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>209.9624545164483</v>
+        <v>230.2640152925681</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>142.112888928247</v>
+        <v>149.8736045303181</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>65.89686940445439</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3075,7 +3075,7 @@
         <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
+        <v>24.16670148773948</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.81130881880213</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.73318560862312</v>
+        <v>1.806415775814131</v>
       </c>
       <c r="C2" t="n">
-        <v>5.14926670877452</v>
+        <v>3.154355373745001</v>
       </c>
       <c r="D2" t="n">
-        <v>13.99186828092554</v>
+        <v>9.367836593923064</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.02212253330795</v>
+        <v>10.38198197241002</v>
       </c>
       <c r="C3" t="n">
-        <v>22.22185928562655</v>
+        <v>24.37188675792707</v>
       </c>
       <c r="D3" t="n">
-        <v>80.76347488986386</v>
+        <v>68.35418390818417</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.66501271533614</v>
+        <v>29.15005283449629</v>
       </c>
       <c r="C4" t="n">
-        <v>52.95252592396021</v>
+        <v>102.0507103610475</v>
       </c>
       <c r="D4" t="n">
-        <v>167.0767695518349</v>
+        <v>151.7742680857399</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.80226177194822</v>
+        <v>46.48575379608648</v>
       </c>
       <c r="C5" t="n">
-        <v>159.288565014045</v>
+        <v>240.6018186182871</v>
       </c>
       <c r="D5" t="n">
-        <v>154.1098458741431</v>
+        <v>141.3471257189345</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>259.0194055499572</v>
+        <v>330.0635781677777</v>
       </c>
       <c r="D6" t="n">
-        <v>79.89953691012668</v>
+        <v>76.11588125795947</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>258.3508353633651</v>
+        <v>287.9947072930975</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>180.0819813899924</v>
+        <v>192.5158160642783</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>76.21405602838412</v>
+        <v>72.22030636750809</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.40157586876595</v>
+        <v>2.208932334555323</v>
       </c>
       <c r="C2" t="n">
-        <v>4.406083696659685</v>
+        <v>7.569274799742908</v>
       </c>
       <c r="D2" t="n">
-        <v>14.96281676042564</v>
+        <v>16.70541893546373</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.77744637077224</v>
+        <v>8.364490440182825</v>
       </c>
       <c r="C3" t="n">
-        <v>21.21065915025234</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D3" t="n">
-        <v>74.29375751887737</v>
+        <v>62.05136364691965</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.45407582764332</v>
+        <v>24.69586350032851</v>
       </c>
       <c r="C4" t="n">
-        <v>53.37369568908209</v>
+        <v>83.34056261351174</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1743634851829</v>
+        <v>149.1834358942326</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.92498023497909</v>
+        <v>45.33220024359647</v>
       </c>
       <c r="C5" t="n">
-        <v>132.2414157620454</v>
+        <v>218.1197961910351</v>
       </c>
       <c r="D5" t="n">
-        <v>171.8794793210103</v>
+        <v>157.275982220339</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.88945739117695</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="C6" t="n">
-        <v>260.1867035703067</v>
+        <v>351.4774590928092</v>
       </c>
       <c r="D6" t="n">
-        <v>99.66309994431923</v>
+        <v>94.55113964830608</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.90822410408209</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="C7" t="n">
-        <v>305.5414840111008</v>
+        <v>364.2902483809342</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>243.4194345294754</v>
+        <v>261.9450137086127</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>131.2390513560093</v>
+        <v>130.4624889219501</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>52.95547116707295</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.831982273853553</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C2" t="n">
-        <v>9.205848222722341</v>
+        <v>9.896016858807849</v>
       </c>
       <c r="D2" t="n">
-        <v>8.981027998449822</v>
+        <v>7.082327938436491</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.863177216211199</v>
+        <v>1.614974973486003</v>
       </c>
       <c r="C2" t="n">
-        <v>2.503456645829366</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="D2" t="n">
-        <v>11.01324574624072</v>
+        <v>12.42794418806037</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.92180434102552</v>
+        <v>11.07411410390402</v>
       </c>
       <c r="C3" t="n">
-        <v>23.23305942100077</v>
+        <v>25.07383636646354</v>
       </c>
       <c r="D3" t="n">
-        <v>80.45422436302611</v>
+        <v>68.64870821945821</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.22054304721959</v>
+        <v>34.395530818287</v>
       </c>
       <c r="C4" t="n">
-        <v>78.18442367080749</v>
+        <v>120.4928409853238</v>
       </c>
       <c r="D4" t="n">
-        <v>170.7269075162246</v>
+        <v>151.3786237609284</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.43604451606839</v>
+        <v>28.37250865273283</v>
       </c>
       <c r="C5" t="n">
-        <v>210.7076010239717</v>
+        <v>310.4040803902353</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1652246562084</v>
+        <v>142.0343491119073</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.50696703048563</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>252.2168757072311</v>
+        <v>301.9276707117684</v>
       </c>
       <c r="D6" t="n">
-        <v>79.37626538376313</v>
+        <v>74.22405343187586</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>171.1559312629804</v>
+        <v>184.2112122340545</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>96.71687508387453</v>
+        <v>96.13273519984767</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.991426312569037</v>
+        <v>5.488951414443917</v>
       </c>
       <c r="C2" t="n">
-        <v>5.045201452124359</v>
+        <v>4.772275590343745</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67141761871358</v>
+        <v>15.50572324087412</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51023106876786</v>
+        <v>9.576948854927634</v>
       </c>
       <c r="C3" t="n">
-        <v>23.19869825135213</v>
+        <v>24.93639168786898</v>
       </c>
       <c r="D3" t="n">
-        <v>10.6814150222053</v>
+        <v>9.086075002804231</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39770697654635</v>
+        <v>13.39831384864168</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14093652427208</v>
+        <v>70.14411367818292</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576200820770159</v>
+        <v>1.576272217487257</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.150248456478768</v>
+        <v>4.583780031128358</v>
       </c>
       <c r="C2" t="n">
-        <v>4.876340846993907</v>
+        <v>4.097814917526186</v>
       </c>
       <c r="D2" t="n">
-        <v>19.12051828791088</v>
+        <v>16.97245431101886</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.35930396422111</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="C3" t="n">
-        <v>20.99467465531804</v>
+        <v>20.97994843975434</v>
       </c>
       <c r="D3" t="n">
-        <v>18.74156367407161</v>
+        <v>19.91475218064655</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.82126516456485</v>
+        <v>11.25671917689393</v>
       </c>
       <c r="C4" t="n">
-        <v>35.90153179660161</v>
+        <v>38.51788942841936</v>
       </c>
       <c r="D4" t="n">
-        <v>20.66284393128262</v>
+        <v>19.83326712119406</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43981033656094</v>
+        <v>15.44136238440258</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1378892460768</v>
+        <v>86.14654803929862</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250486386644408</v>
+        <v>3.250813133558438</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.126105674500097</v>
+        <v>4.206788912697583</v>
       </c>
       <c r="C2" t="n">
-        <v>4.409028939772425</v>
+        <v>5.529203070318036</v>
       </c>
       <c r="D2" t="n">
-        <v>17.71171033231671</v>
+        <v>18.1750952487212</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.8067599331794</v>
+        <v>15.58524480491811</v>
       </c>
       <c r="C3" t="n">
-        <v>19.76749002500953</v>
+        <v>17.92671307954676</v>
       </c>
       <c r="D3" t="n">
-        <v>29.68805057642355</v>
+        <v>28.86829124337746</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.8557495074005</v>
+        <v>21.46689530106076</v>
       </c>
       <c r="C4" t="n">
-        <v>45.72882631611218</v>
+        <v>46.78813208899449</v>
       </c>
       <c r="D4" t="n">
-        <v>25.41057582902019</v>
+        <v>25.35952494839936</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.48077863764046</v>
+        <v>10.35743827980385</v>
       </c>
       <c r="C5" t="n">
-        <v>40.07985002587604</v>
+        <v>42.85328729037328</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09056713516474</v>
+        <v>29.57514959043517</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73145282881838</v>
+        <v>16.73561813976803</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0618622557921</v>
+        <v>102.087270652585</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182863207204594</v>
+        <v>5.02068544193041</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.910121179565798</v>
+        <v>4.648575379608647</v>
       </c>
       <c r="C2" t="n">
-        <v>5.863979037466199</v>
+        <v>7.913868243933538</v>
       </c>
       <c r="D2" t="n">
-        <v>28.71906559233194</v>
+        <v>20.10913822608742</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.45962215650353</v>
+        <v>14.94220005863645</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2212373908208</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="D3" t="n">
-        <v>36.54555829058751</v>
+        <v>36.26085145635594</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>26.27844079957437</v>
       </c>
       <c r="C4" t="n">
-        <v>47.82191242156638</v>
+        <v>45.26936839052468</v>
       </c>
       <c r="D4" t="n">
-        <v>34.07646281440679</v>
+        <v>33.6425303291297</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.97414006898687</v>
+        <v>21.18120671912494</v>
       </c>
       <c r="C5" t="n">
-        <v>63.66633862040567</v>
+        <v>66.83247496660162</v>
       </c>
       <c r="D5" t="n">
-        <v>32.12769362147687</v>
+        <v>31.68590715456581</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.84027822384404</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>39.28561613314037</v>
+        <v>41.53970886209105</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
         <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05560599644867</v>
+        <v>18.06335589195402</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7913343577842</v>
+        <v>117.8418931998905</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018535332149556</v>
+        <v>6.881278435030103</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.185992284459152</v>
+        <v>5.019676011813941</v>
       </c>
       <c r="C2" t="n">
-        <v>8.512734343524093</v>
+        <v>13.75035834568082</v>
       </c>
       <c r="D2" t="n">
-        <v>28.65623373926015</v>
+        <v>27.41726813650067</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09851892778995</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C3" t="n">
-        <v>19.57114048416017</v>
+        <v>24.55351008321273</v>
       </c>
       <c r="D3" t="n">
-        <v>47.26133448244146</v>
+        <v>40.90451809744336</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.35050929261189</v>
+        <v>20.07575880414303</v>
       </c>
       <c r="C4" t="n">
-        <v>38.96458463385165</v>
+        <v>39.71758512300897</v>
       </c>
       <c r="D4" t="n">
-        <v>38.51788942841936</v>
+        <v>37.81593981988289</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.06540154775282</v>
+        <v>18.60411899547706</v>
       </c>
       <c r="C5" t="n">
-        <v>56.72047361285948</v>
+        <v>56.54866776461629</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>48.58374864006191</v>
+        <v>50.83784136901259</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15237618280328</v>
+        <v>26.40999499194344</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055798046380699</v>
+        <v>7.06106950917528</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14810668481906</v>
+        <v>66.19752664851825</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409873778987937</v>
+        <v>5.29580213188146</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.564545987670921</v>
+        <v>4.090942683596459</v>
       </c>
       <c r="C2" t="n">
-        <v>6.181083545937918</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="D2" t="n">
-        <v>29.36800082483909</v>
+        <v>34.10493349782995</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36144738607885</v>
+        <v>16.1595672119025</v>
       </c>
       <c r="C3" t="n">
-        <v>28.40196108386023</v>
+        <v>43.68286410046183</v>
       </c>
       <c r="D3" t="n">
-        <v>59.91115365166161</v>
+        <v>54.75206946584461</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.65980087717864</v>
+        <v>24.56823629877643</v>
       </c>
       <c r="C4" t="n">
-        <v>45.35870743161113</v>
+        <v>53.70552641311752</v>
       </c>
       <c r="D4" t="n">
-        <v>53.97354353637689</v>
+        <v>51.1402196619206</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.12202411942965</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="C5" t="n">
-        <v>65.65437772150545</v>
+        <v>67.15154297048184</v>
       </c>
       <c r="D5" t="n">
-        <v>37.69911184307752</v>
+        <v>37.50276230222816</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.48558956517046</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>73.53977528201584</v>
+        <v>74.3045567436241</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.75584792127881</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>51.92169083450106</v>
+        <v>54.37704184282233</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.278173582010384</v>
+        <v>7.285018549430449</v>
       </c>
       <c r="C21" t="n">
-        <v>75.51105091335774</v>
+        <v>75.58206745034092</v>
       </c>
       <c r="D21" t="n">
-        <v>5.458630186507787</v>
+        <v>6.374391230751643</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.159485096444488</v>
+        <v>3.95840674352314</v>
       </c>
       <c r="C2" t="n">
-        <v>4.077198215737003</v>
+        <v>3.73653176236336</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90836297280233</v>
+        <v>31.68394365915731</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75276380944582</v>
+        <v>15.0354660905399</v>
       </c>
       <c r="C3" t="n">
-        <v>25.76596849795754</v>
+        <v>30.05129722699487</v>
       </c>
       <c r="D3" t="n">
-        <v>69.50282872215294</v>
+        <v>69.33102287390976</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.56519324467246</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="C4" t="n">
-        <v>60.54634441630929</v>
+        <v>86.49295449184824</v>
       </c>
       <c r="D4" t="n">
-        <v>71.86687719397926</v>
+        <v>67.09361985593127</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.19689898685967</v>
+        <v>31.95588777323368</v>
       </c>
       <c r="C5" t="n">
-        <v>76.08544707912782</v>
+        <v>84.87208903213677</v>
       </c>
       <c r="D5" t="n">
-        <v>48.22835597112457</v>
+        <v>47.09934611124073</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.91705983342032</v>
+        <v>27.4113776502752</v>
       </c>
       <c r="C6" t="n">
-        <v>90.00270253453061</v>
+        <v>92.69956347809659</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>82.28420208374216</v>
+        <v>84.08080038251383</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>50.31947858117027</v>
+        <v>52.5725895624167</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487990609275721</v>
+        <v>7.495431604083349</v>
       </c>
       <c r="C21" t="n">
-        <v>84.23989435435186</v>
+        <v>85.26053449644809</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551991783116256</v>
+        <v>7.495431604083349</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497632686876</v>
+        <v>10.84497648805088</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907192328044</v>
+        <v>37.78907248491583</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.871432108472673</v>
+        <v>4.456152829576273</v>
       </c>
       <c r="C2" t="n">
-        <v>6.539421457988005</v>
+        <v>7.522150909939061</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41530464109218</v>
+        <v>20.8994451280061</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16661937228147</v>
+        <v>15.15327581504952</v>
       </c>
       <c r="C3" t="n">
-        <v>21.49045724596268</v>
+        <v>18.21632865229957</v>
       </c>
       <c r="D3" t="n">
-        <v>77.38626278725484</v>
+        <v>67.77986150119979</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.53744226704628</v>
+        <v>31.72812230584842</v>
       </c>
       <c r="C4" t="n">
-        <v>79.52450928710439</v>
+        <v>50.45103277353934</v>
       </c>
       <c r="D4" t="n">
-        <v>83.95317318096176</v>
+        <v>90.98543198648164</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.3064127613788</v>
+        <v>39.46625771072178</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5346962837079</v>
+        <v>98.32203258031808</v>
       </c>
       <c r="D5" t="n">
-        <v>59.81297888123694</v>
+        <v>69.43410638285567</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.74347041621788</v>
+        <v>36.79001346894498</v>
       </c>
       <c r="C6" t="n">
-        <v>113.5499212208904</v>
+        <v>134.4405306195582</v>
       </c>
       <c r="D6" t="n">
-        <v>43.63279496754524</v>
+        <v>46.89317909334891</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="C7" t="n">
-        <v>110.3710221545391</v>
+        <v>133.7866866485298</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>82.86441497695203</v>
+        <v>91.45961612763286</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691284669437996</v>
+        <v>7.675486965003818</v>
       </c>
       <c r="C21" t="n">
-        <v>94.21823720061545</v>
+        <v>93.06527945067128</v>
       </c>
       <c r="D21" t="n">
-        <v>8.652695253117745</v>
+        <v>7.675486965003818</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.156138942704248</v>
+        <v>5.7402788267311</v>
       </c>
       <c r="C2" t="n">
-        <v>18.12404436810036</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D2" t="n">
-        <v>29.68216009019806</v>
+        <v>18.38322576202152</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18272824617692</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C3" t="n">
-        <v>23.39013905368026</v>
+        <v>23.78774687390022</v>
       </c>
       <c r="D3" t="n">
-        <v>80.30205346886785</v>
+        <v>68.21673922958962</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="C4" t="n">
-        <v>65.75353423963438</v>
+        <v>47.42626809675492</v>
       </c>
       <c r="D4" t="n">
-        <v>100.5319466625776</v>
+        <v>102.1272866819787</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.71169463678348</v>
+        <v>43.02509313861647</v>
       </c>
       <c r="C5" t="n">
-        <v>135.2848336452105</v>
+        <v>95.64677008624551</v>
       </c>
       <c r="D5" t="n">
-        <v>73.01748550335654</v>
+        <v>82.85950623843081</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.50574860306991</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="C6" t="n">
-        <v>152.2317625159189</v>
+        <v>143.8996697499763</v>
       </c>
       <c r="D6" t="n">
-        <v>51.40136455125026</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.29695513723482</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7211305365236</v>
+        <v>163.5503317981804</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.44351328260808</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="C8" t="n">
-        <v>112.5721005074605</v>
+        <v>131.4314739060417</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>79.20936827404113</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1265,7 +1265,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.872104724529456</v>
+        <v>7.856163774148468</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3373614188829</v>
+        <v>101.1481085921615</v>
       </c>
       <c r="D21" t="n">
-        <v>9.840130905661821</v>
+        <v>8.838184245917025</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.428483967408114</v>
+        <v>6.30674725208151</v>
       </c>
       <c r="C2" t="n">
-        <v>17.90805987316607</v>
+        <v>20.27701708351362</v>
       </c>
       <c r="D2" t="n">
-        <v>26.57394685855266</v>
+        <v>21.13310108161684</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85522542358599</v>
+        <v>16.63080610994097</v>
       </c>
       <c r="C3" t="n">
-        <v>45.69544689416779</v>
+        <v>42.29369109895259</v>
       </c>
       <c r="D3" t="n">
-        <v>83.3356538749905</v>
+        <v>66.77357010434682</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6695772964921</v>
+        <v>28.8692729910817</v>
       </c>
       <c r="C4" t="n">
-        <v>61.61841290934681</v>
+        <v>52.79937328209771</v>
       </c>
       <c r="D4" t="n">
-        <v>112.0949711231966</v>
+        <v>110.5762074247267</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.66889864842413</v>
+        <v>43.81049130201392</v>
       </c>
       <c r="C5" t="n">
-        <v>127.430852011236</v>
+        <v>90.86075002804232</v>
       </c>
       <c r="D5" t="n">
-        <v>87.4000893705723</v>
+        <v>95.89220701230721</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.97368240509714</v>
+        <v>50.11331156327844</v>
       </c>
       <c r="C6" t="n">
-        <v>179.60288851032</v>
+        <v>146.516027381794</v>
       </c>
       <c r="D6" t="n">
-        <v>60.53849043467533</v>
+        <v>67.18001365390501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.42346172236242</v>
+        <v>42.51949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>171.3954777028166</v>
+        <v>184.2710988440136</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.28629478120835</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="C8" t="n">
-        <v>141.9459918185251</v>
+        <v>167.8984923802895</v>
       </c>
       <c r="D8" t="n">
         <v>40.55599766243574</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97812381306608</v>
+        <v>13.86718632248619</v>
       </c>
       <c r="C9" t="n">
-        <v>102.8390537675576</v>
+        <v>114.8203027501857</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>61.78138302825178</v>
+        <v>65.0555116219149</v>
       </c>
       <c r="D10" t="n">
         <v>36.44247478164161</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>40.69246059332603</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036514504153706</v>
+        <v>8.022034179198707</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5020744321135</v>
+        <v>109.3002156915824</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05020744321135</v>
+        <v>10.02754272399839</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.85121631731099</v>
+        <v>5.760895528520283</v>
       </c>
       <c r="C2" t="n">
-        <v>12.17661677577319</v>
+        <v>13.7876647584422</v>
       </c>
       <c r="D2" t="n">
-        <v>22.05888916672158</v>
+        <v>17.41914951645116</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.06063167795183</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="C3" t="n">
-        <v>64.39283192154829</v>
+        <v>60.95180621816323</v>
       </c>
       <c r="D3" t="n">
-        <v>89.2457750545563</v>
+        <v>74.19067400993146</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.53972455762427</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="C4" t="n">
-        <v>97.32850390362029</v>
+        <v>74.7512519490564</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5777289517787</v>
+        <v>107.7045953898048</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.45810062945155</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>107.3050240741764</v>
+        <v>87.54735152620933</v>
       </c>
       <c r="D5" t="n">
-        <v>59.66571672559991</v>
+        <v>65.89981464756715</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.07678160957628</v>
+        <v>26.40508625342222</v>
       </c>
       <c r="C6" t="n">
-        <v>112.8656430710303</v>
+        <v>121.3587424604695</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>31.43654323768712</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>99.77109219178635</v>
+        <v>118.0365082292982</v>
       </c>
       <c r="D7" t="n">
         <v>28.50602634051038</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>75.77128781376882</v>
+        <v>84.61683462903258</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
         <v>27.73437264497238</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.496003574822891</v>
+        <v>3.585342615909352</v>
       </c>
       <c r="C2" t="n">
-        <v>5.432991795301848</v>
+        <v>5.730461349688632</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24261485613598</v>
+        <v>12.87071240267568</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07674055184727</v>
+        <v>20.50870954171587</v>
       </c>
       <c r="C3" t="n">
-        <v>56.98063675448488</v>
+        <v>58.55143308127977</v>
       </c>
       <c r="D3" t="n">
-        <v>87.82224088339842</v>
+        <v>71.66758241001716</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.84000048640355</v>
+        <v>28.57573042751191</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3283903970958</v>
+        <v>113.9200401053914</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7480953884279</v>
+        <v>119.5739251341488</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.25608158655496</v>
+        <v>31.29320807286709</v>
       </c>
       <c r="C5" t="n">
-        <v>141.3716694115407</v>
+        <v>113.1218792218388</v>
       </c>
       <c r="D5" t="n">
-        <v>76.62540831646356</v>
+        <v>82.78587516061229</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.66547037922588</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>141.5248220534032</v>
+        <v>135.2455637370406</v>
       </c>
       <c r="D6" t="n">
-        <v>37.0315234041897</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>125.5822210841392</v>
+        <v>145.5244622005047</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>97.9686034067892</v>
+        <v>110.3189895262141</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>52.25155806312797</v>
+        <v>55.1359328182051</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.158282364561989</v>
+        <v>3.579452129683871</v>
       </c>
       <c r="C2" t="n">
-        <v>9.185231520933158</v>
+        <v>7.241371066524473</v>
       </c>
       <c r="D2" t="n">
-        <v>19.5760492226814</v>
+        <v>15.32115467247572</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96321767105314</v>
+        <v>16.47372647726148</v>
       </c>
       <c r="C3" t="n">
-        <v>37.88564390688441</v>
+        <v>39.46134897220054</v>
       </c>
       <c r="D3" t="n">
-        <v>80.34132337703772</v>
+        <v>65.85563600087605</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.40454647407447</v>
+        <v>33.47661496711199</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0926320793563</v>
+        <v>130.3073727846792</v>
       </c>
       <c r="D4" t="n">
-        <v>134.6339349172949</v>
+        <v>126.8231501823072</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.26299487821369</v>
+        <v>36.74190783143688</v>
       </c>
       <c r="C5" t="n">
-        <v>189.6491127678776</v>
+        <v>160.589380722172</v>
       </c>
       <c r="D5" t="n">
-        <v>98.17477042468106</v>
+        <v>102.8626157124596</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="C6" t="n">
-        <v>180.0456567249353</v>
+        <v>157.9072459941697</v>
       </c>
       <c r="D6" t="n">
-        <v>49.26802678992194</v>
+        <v>52.68941753922207</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3706719683032</v>
+        <v>170.8564982131851</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>129.7625028088221</v>
+        <v>148.4549790976814</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>82.20468051969816</v>
+        <v>89.63749238855074</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.890846078379357</v>
+        <v>2.112721059539136</v>
       </c>
       <c r="C2" t="n">
-        <v>4.391357481095983</v>
+        <v>3.418445506187394</v>
       </c>
       <c r="D2" t="n">
-        <v>13.67181852934108</v>
+        <v>10.68534201302228</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.36926030998382</v>
+        <v>16.3608254912731</v>
       </c>
       <c r="C3" t="n">
-        <v>39.42698780255191</v>
+        <v>37.16405934426301</v>
       </c>
       <c r="D3" t="n">
-        <v>80.36095833112267</v>
+        <v>65.49729808882596</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.65904011365264</v>
+        <v>36.7949222074662</v>
       </c>
       <c r="C4" t="n">
-        <v>135.9229696529709</v>
+        <v>131.0603732738365</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8996697499762</v>
+        <v>133.3959510622396</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>38.7054032399305</v>
       </c>
       <c r="C5" t="n">
-        <v>232.944186525162</v>
+        <v>205.0380080319464</v>
       </c>
       <c r="D5" t="n">
-        <v>103.9916255723434</v>
+        <v>108.2376843932109</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>30.14849024971531</v>
       </c>
       <c r="C6" t="n">
-        <v>216.2721470116427</v>
+        <v>195.2205309894783</v>
       </c>
       <c r="D6" t="n">
-        <v>48.5434969841878</v>
+        <v>51.64287448649497</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>171.0960446530214</v>
+        <v>184.2112122340545</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>98.71964040053801</v>
+        <v>111.1534750748239</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
         <v>31.8390597964283</v>
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.679189484889545</v>
+        <v>2.288453898599315</v>
       </c>
       <c r="C2" t="n">
-        <v>4.857687640613218</v>
+        <v>5.008876787067226</v>
       </c>
       <c r="D2" t="n">
-        <v>11.55026174046372</v>
+        <v>14.28737433990383</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.1428364432013</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="C3" t="n">
-        <v>28.28415135935061</v>
+        <v>25.02965771977243</v>
       </c>
       <c r="D3" t="n">
-        <v>74.09740797802802</v>
+        <v>60.0829594999048</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.68532631748906</v>
+        <v>34.51039529968388</v>
       </c>
       <c r="C4" t="n">
-        <v>118.9996027271644</v>
+        <v>113.3840058588726</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5025038981128</v>
+        <v>135.0040538017959</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.36870483510285</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="C5" t="n">
-        <v>240.3809253848316</v>
+        <v>223.4948648717864</v>
       </c>
       <c r="D5" t="n">
-        <v>125.6882498361979</v>
+        <v>126.277298458746</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>38.48058301565798</v>
       </c>
       <c r="C6" t="n">
-        <v>286.954054726596</v>
+        <v>253.5854320069512</v>
       </c>
       <c r="D6" t="n">
-        <v>64.76491430145784</v>
+        <v>67.86429180376503</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>230.2640152925681</v>
+        <v>227.5691178444106</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>149.8736045303181</v>
+        <v>167.1474553865407</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>65.89686940445439</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
         <v>32.61562223048752</v>
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.806415775814131</v>
+        <v>1.606139244147782</v>
       </c>
       <c r="C2" t="n">
-        <v>3.154355373745001</v>
+        <v>2.959969328304133</v>
       </c>
       <c r="D2" t="n">
-        <v>9.367836593923064</v>
+        <v>11.30384306669777</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.38198197241002</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C3" t="n">
-        <v>24.37188675792707</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="D3" t="n">
-        <v>68.35418390818417</v>
+        <v>58.75269136065037</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.15005283449629</v>
+        <v>30.88578277560466</v>
       </c>
       <c r="C4" t="n">
-        <v>102.0507103610475</v>
+        <v>94.80148531288899</v>
       </c>
       <c r="D4" t="n">
-        <v>151.7742680857399</v>
+        <v>134.8381384397782</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.48575379608648</v>
+        <v>49.65189014228245</v>
       </c>
       <c r="C5" t="n">
-        <v>240.6018186182871</v>
+        <v>225.4829039728862</v>
       </c>
       <c r="D5" t="n">
-        <v>141.3471257189345</v>
+        <v>137.7146592132214</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>44.71958967614647</v>
       </c>
       <c r="C6" t="n">
-        <v>330.0635781677777</v>
+        <v>297.9427567802306</v>
       </c>
       <c r="D6" t="n">
-        <v>76.11588125795947</v>
+        <v>81.06683493047613</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>287.9947072930975</v>
+        <v>278.2930764797306</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>44.31609136970101</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>192.5158160642783</v>
+        <v>206.4517247260617</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>80.76249314215958</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.208932334555323</v>
+        <v>2.475967710110456</v>
       </c>
       <c r="C2" t="n">
-        <v>7.569274799742908</v>
+        <v>9.122399667861362</v>
       </c>
       <c r="D2" t="n">
-        <v>16.70541893546373</v>
+        <v>14.47292465600648</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.364490440182825</v>
+        <v>8.035604959260143</v>
       </c>
       <c r="C3" t="n">
-        <v>18.99190933865455</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D3" t="n">
-        <v>62.05136364691965</v>
+        <v>54.72261703471722</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.69586350032851</v>
+        <v>25.64030479181395</v>
       </c>
       <c r="C4" t="n">
-        <v>83.34056261351174</v>
+        <v>77.20169421885643</v>
       </c>
       <c r="D4" t="n">
-        <v>149.1834358942326</v>
+        <v>133.3193747413084</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.33220024359647</v>
+        <v>48.35107443415542</v>
       </c>
       <c r="C5" t="n">
-        <v>218.1197961910351</v>
+        <v>203.3690369347268</v>
       </c>
       <c r="D5" t="n">
-        <v>157.275982220339</v>
+        <v>149.8637870532756</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>53.05168244208915</v>
       </c>
       <c r="C6" t="n">
-        <v>351.4774590928092</v>
+        <v>325.9176576127434</v>
       </c>
       <c r="D6" t="n">
-        <v>94.55113964830608</v>
+        <v>98.09328536522857</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="C7" t="n">
-        <v>364.2902483809342</v>
+        <v>338.0000266089088</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>52.81998998388688</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>261.9450137086127</v>
+        <v>268.53744954263</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>130.4624889219501</v>
+        <v>144.1078002632765</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>54.37900533823083</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3781,7 +3781,7 @@
         <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.505240214788612</v>
+        <v>4.499349728563132</v>
       </c>
       <c r="C2" t="n">
-        <v>9.896016858807849</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="D2" t="n">
-        <v>7.082327938436491</v>
+        <v>9.710466542705202</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.614974973486003</v>
+        <v>1.789726064841935</v>
       </c>
       <c r="C2" t="n">
-        <v>4.41982816451914</v>
+        <v>5.254313713128929</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42794418806037</v>
+        <v>10.76780882017902</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.07411410390402</v>
+        <v>11.02502671869168</v>
       </c>
       <c r="C3" t="n">
-        <v>25.07383636646354</v>
+        <v>25.4714441866835</v>
       </c>
       <c r="D3" t="n">
-        <v>68.64870821945821</v>
+        <v>60.02896337617122</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.395530818287</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="C4" t="n">
-        <v>120.4928409853238</v>
+        <v>112.0183948022653</v>
       </c>
       <c r="D4" t="n">
-        <v>151.3786237609284</v>
+        <v>137.7225131948553</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.37250865273283</v>
+        <v>30.77779052813751</v>
       </c>
       <c r="C5" t="n">
-        <v>310.4040803902353</v>
+        <v>288.5356502781376</v>
       </c>
       <c r="D5" t="n">
-        <v>142.0343491119073</v>
+        <v>137.1992416684918</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.8994040702771</v>
+        <v>17.22770871412303</v>
       </c>
       <c r="C6" t="n">
-        <v>301.9276707117684</v>
+        <v>283.2911540420512</v>
       </c>
       <c r="D6" t="n">
-        <v>74.22405343187586</v>
+        <v>78.32972233103602</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>184.2112122340545</v>
+        <v>188.8224812009018</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>96.13273519984767</v>
+        <v>106.2300103380261</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4389,7 +4389,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.488951414443917</v>
+        <v>6.015168183920207</v>
       </c>
       <c r="C2" t="n">
-        <v>4.772275590343745</v>
+        <v>8.44597549963531</v>
       </c>
       <c r="D2" t="n">
-        <v>15.50572324087412</v>
+        <v>13.75330358879357</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.576948854927634</v>
+        <v>9.562222639363933</v>
       </c>
       <c r="C3" t="n">
-        <v>24.93639168786898</v>
+        <v>23.84174299763379</v>
       </c>
       <c r="D3" t="n">
-        <v>9.086075002804231</v>
+        <v>11.29500733735955</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39831384864168</v>
+        <v>13.39793808950696</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14411367818292</v>
+        <v>70.14214646859524</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576272217487257</v>
+        <v>1.57622801053023</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.583780031128358</v>
+        <v>4.206788912697583</v>
       </c>
       <c r="C2" t="n">
-        <v>4.097814917526186</v>
+        <v>5.799183688985909</v>
       </c>
       <c r="D2" t="n">
-        <v>16.97245431101886</v>
+        <v>22.47711368873073</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.19254572321939</v>
+        <v>16.26265072084841</v>
       </c>
       <c r="C3" t="n">
-        <v>20.97994843975434</v>
+        <v>29.53097094374406</v>
       </c>
       <c r="D3" t="n">
-        <v>19.91475218064655</v>
+        <v>20.11601046001715</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.25671917689393</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="C4" t="n">
-        <v>38.51788942841936</v>
+        <v>36.88426124855267</v>
       </c>
       <c r="D4" t="n">
-        <v>19.83326712119406</v>
+        <v>20.99467465531804</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44136238440258</v>
+        <v>15.44030009547687</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14654803929862</v>
+        <v>86.14062158529204</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250813133558438</v>
+        <v>3.250589493784605</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.206788912697583</v>
+        <v>5.026548245743669</v>
       </c>
       <c r="C2" t="n">
-        <v>5.529203070318036</v>
+        <v>7.596763735461819</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1750952487212</v>
+        <v>30.74146586308037</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58524480491811</v>
+        <v>15.31035544772901</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92671307954676</v>
+        <v>25.30945581548277</v>
       </c>
       <c r="D3" t="n">
-        <v>28.86829124337746</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.46689530106076</v>
+        <v>22.71764187627119</v>
       </c>
       <c r="C4" t="n">
-        <v>46.78813208899449</v>
+        <v>58.70851271395926</v>
       </c>
       <c r="D4" t="n">
-        <v>25.35952494839936</v>
+        <v>26.35501712050563</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.35743827980385</v>
+        <v>10.16108873895449</v>
       </c>
       <c r="C5" t="n">
-        <v>42.85328729037328</v>
+        <v>41.13522880794136</v>
       </c>
       <c r="D5" t="n">
-        <v>29.57514959043517</v>
+        <v>30.2132855981956</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73561813976803</v>
+        <v>16.73138997457471</v>
       </c>
       <c r="C21" t="n">
-        <v>102.087270652585</v>
+        <v>102.0614788449057</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02068544193041</v>
+        <v>4.182847493643678</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.648575379608647</v>
+        <v>5.14926670877452</v>
       </c>
       <c r="C2" t="n">
-        <v>7.913868243933538</v>
+        <v>4.294164458375548</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10913822608742</v>
+        <v>26.67801211520282</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.94220005863645</v>
+        <v>16.29210315197582</v>
       </c>
       <c r="C3" t="n">
-        <v>19.95402208881642</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D3" t="n">
-        <v>36.26085145635594</v>
+        <v>49.35736583100839</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.27844079957437</v>
+        <v>26.24015263910875</v>
       </c>
       <c r="C4" t="n">
-        <v>45.26936839052468</v>
+        <v>60.66120889770617</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6425303291297</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.18120671912494</v>
+        <v>22.08932334555324</v>
       </c>
       <c r="C5" t="n">
-        <v>66.83247496660162</v>
+        <v>77.45989386507335</v>
       </c>
       <c r="D5" t="n">
-        <v>31.68590715456581</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.06291396852981</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53970886209105</v>
+        <v>39.52712606838509</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06335589195402</v>
+        <v>18.05123382257515</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8418931998905</v>
+        <v>117.7628111282283</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881278435030103</v>
+        <v>6.017077940858382</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.019676011813941</v>
+        <v>4.960771149559132</v>
       </c>
       <c r="C2" t="n">
-        <v>13.75035834568082</v>
+        <v>6.455972903127026</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41726813650067</v>
+        <v>20.7148765596077</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78864650614645</v>
+        <v>15.17291076913446</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55351008321273</v>
+        <v>20.2534551386117</v>
       </c>
       <c r="D3" t="n">
-        <v>40.90451809744336</v>
+        <v>55.18403845571321</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.07575880414303</v>
+        <v>21.27545449873262</v>
       </c>
       <c r="C4" t="n">
-        <v>39.71758512300897</v>
+        <v>54.48405234258524</v>
       </c>
       <c r="D4" t="n">
-        <v>37.81593981988289</v>
+        <v>45.57567367424968</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.60411899547706</v>
+        <v>18.70229376590174</v>
       </c>
       <c r="C5" t="n">
-        <v>56.54866776461629</v>
+        <v>71.34851440613696</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>30.58144098728815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>50.83784136901259</v>
+        <v>55.4667817945363</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>31.07427833482005</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>26.40999499194344</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06106950917528</v>
+        <v>7.052540542228805</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19752664851825</v>
+        <v>66.11756758339504</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29580213188146</v>
+        <v>4.407837838893003</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.090942683596459</v>
+        <v>5.293583621298801</v>
       </c>
       <c r="C2" t="n">
-        <v>5.449681506274044</v>
+        <v>3.981968688425063</v>
       </c>
       <c r="D2" t="n">
-        <v>34.10493349782995</v>
+        <v>23.40290177383547</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1595672119025</v>
+        <v>16.52281386247382</v>
       </c>
       <c r="C3" t="n">
-        <v>43.68286410046183</v>
+        <v>23.45886139297754</v>
       </c>
       <c r="D3" t="n">
-        <v>54.75206946584461</v>
+        <v>59.248473951295</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.56823629877643</v>
+        <v>26.35501712050563</v>
       </c>
       <c r="C4" t="n">
-        <v>53.70552641311752</v>
+        <v>52.23781359526853</v>
       </c>
       <c r="D4" t="n">
-        <v>51.1402196619206</v>
+        <v>63.48177005200726</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.35363446217388</v>
+        <v>26.5808190924824</v>
       </c>
       <c r="C5" t="n">
-        <v>67.15154297048184</v>
+        <v>89.43721585688444</v>
       </c>
       <c r="D5" t="n">
-        <v>37.50276230222816</v>
+        <v>41.13522880794136</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.24029150782899</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>74.3045567436241</v>
+        <v>89.64043763166353</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>54.37704184282233</v>
+        <v>57.19171251089794</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>28.62285431731576</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285018549430449</v>
+        <v>7.273026995915334</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58206745034092</v>
+        <v>75.4576550826216</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374391230751643</v>
+        <v>5.4547702469365</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.95840674352314</v>
+        <v>3.849432748351743</v>
       </c>
       <c r="C2" t="n">
-        <v>3.73653176236336</v>
+        <v>4.57985304031137</v>
       </c>
       <c r="D2" t="n">
-        <v>31.68394365915731</v>
+        <v>23.92420980479052</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0354660905399</v>
+        <v>17.55364895193297</v>
       </c>
       <c r="C3" t="n">
-        <v>30.05129722699487</v>
+        <v>18.85446466005999</v>
       </c>
       <c r="D3" t="n">
-        <v>69.33102287390976</v>
+        <v>64.2210260733051</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.42257778564941</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>86.49295449184824</v>
+        <v>55.51783267515713</v>
       </c>
       <c r="D4" t="n">
-        <v>67.09361985593127</v>
+        <v>78.93742415996479</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.95588777323368</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>84.87208903213677</v>
+        <v>93.5850999073272</v>
       </c>
       <c r="D5" t="n">
-        <v>47.09934611124073</v>
+        <v>54.24156065963628</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.4113776502752</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>92.69956347809659</v>
+        <v>118.7021331727776</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>39.84913931537804</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>84.08080038251383</v>
+        <v>96.11800898428396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>52.5725895624167</v>
+        <v>53.90776644019235</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495431604083349</v>
+        <v>7.480973076091251</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26053449644809</v>
+        <v>84.16094710602658</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495431604083349</v>
+        <v>6.545851441579845</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_70_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648805088</v>
+        <v>10.84497656319582</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907248491583</v>
+        <v>37.78907274675667</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.456152829576273</v>
+        <v>0.6695519342963246</v>
       </c>
       <c r="C2" t="n">
-        <v>7.522150909939061</v>
+        <v>2.408227118517426</v>
       </c>
       <c r="D2" t="n">
-        <v>20.8994451280061</v>
+        <v>16.93907488907447</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>6.459899893944012</v>
       </c>
       <c r="C3" t="n">
-        <v>18.21632865229957</v>
+        <v>30.5323536020758</v>
       </c>
       <c r="D3" t="n">
-        <v>67.77986150119979</v>
+        <v>57.81021356457343</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.72812230584842</v>
+        <v>13.42638160327938</v>
       </c>
       <c r="C4" t="n">
-        <v>50.45103277353934</v>
+        <v>122.0116046837936</v>
       </c>
       <c r="D4" t="n">
-        <v>90.98543198648164</v>
+        <v>60.68673433801658</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.46625771072178</v>
+        <v>12.49273953654066</v>
       </c>
       <c r="C5" t="n">
-        <v>98.32203258031808</v>
+        <v>140.3899217072939</v>
       </c>
       <c r="D5" t="n">
-        <v>69.43410638285567</v>
+        <v>44.17864669110647</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.79001346894498</v>
+        <v>8.976119259928589</v>
       </c>
       <c r="C6" t="n">
-        <v>134.4405306195582</v>
+        <v>68.62907326537329</v>
       </c>
       <c r="D6" t="n">
-        <v>46.89317909334891</v>
+        <v>29.42396044398116</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>33.95570784678443</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>91.45961612763286</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.675486965003818</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.06527945067128</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.675486965003818</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.7402788267311</v>
+        <v>0.7215845626214056</v>
       </c>
       <c r="C2" t="n">
-        <v>16.28621266575034</v>
+        <v>9.986337647598555</v>
       </c>
       <c r="D2" t="n">
-        <v>18.38322576202152</v>
+        <v>21.6063034750638</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.97165248976386</v>
+        <v>4.201880174176348</v>
       </c>
       <c r="C3" t="n">
-        <v>23.78774687390022</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="D3" t="n">
-        <v>68.21673922958962</v>
+        <v>58.50234569606743</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>13.12007631955437</v>
       </c>
       <c r="C4" t="n">
-        <v>47.42626809675492</v>
+        <v>96.14157092918589</v>
       </c>
       <c r="D4" t="n">
-        <v>102.1272866819787</v>
+        <v>75.18518443433348</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.02509313861647</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C5" t="n">
-        <v>95.64677008624551</v>
+        <v>188.5691902932061</v>
       </c>
       <c r="D5" t="n">
-        <v>82.85950623843081</v>
+        <v>55.34602682691395</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>12.96103319146639</v>
       </c>
       <c r="C6" t="n">
-        <v>143.8996697499763</v>
+        <v>149.21288832536</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>36.02523200733671</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.19525428662065</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>163.5503317981804</v>
+        <v>66.95322993422397</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.52696183746906</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>131.4314739060417</v>
+        <v>36.88426124855267</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>79.20936827404113</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.856163774148468</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1481085921615</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.838184245917025</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.30674725208151</v>
+        <v>0.3838633523605028</v>
       </c>
       <c r="C2" t="n">
-        <v>20.27701708351362</v>
+        <v>4.123340357836604</v>
       </c>
       <c r="D2" t="n">
-        <v>21.13310108161684</v>
+        <v>14.53870175219101</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.63080610994097</v>
+        <v>3.877903431774901</v>
       </c>
       <c r="C3" t="n">
-        <v>42.29369109895259</v>
+        <v>29.86967390170921</v>
       </c>
       <c r="D3" t="n">
-        <v>66.77357010434682</v>
+        <v>63.24909584610077</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8692729910817</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C4" t="n">
-        <v>52.79937328209771</v>
+        <v>85.06352983446489</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5762074247267</v>
+        <v>86.08454744688157</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.81049130201392</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>90.86075002804232</v>
+        <v>208.9895425415398</v>
       </c>
       <c r="D5" t="n">
-        <v>95.89220701230721</v>
+        <v>61.99736752318609</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>146.516027381794</v>
+        <v>193.7312197221359</v>
       </c>
       <c r="D6" t="n">
-        <v>67.18001365390501</v>
+        <v>36.87051678069322</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.51949307092936</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>184.2710988440136</v>
+        <v>64.4978789259027</v>
       </c>
       <c r="D7" t="n">
-        <v>47.72962813736718</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8984923802895</v>
+        <v>38.46978379091126</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>114.8203027501857</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>65.0555116219149</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.022034179198707</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3002156915824</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02754272399839</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.760895528520283</v>
+        <v>0.8374307917225292</v>
       </c>
       <c r="C2" t="n">
-        <v>13.7876647584422</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="D2" t="n">
-        <v>17.41914951645116</v>
+        <v>15.21807116352981</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>2.552544031041707</v>
       </c>
       <c r="C3" t="n">
-        <v>60.95180621816323</v>
+        <v>22.13841073076557</v>
       </c>
       <c r="D3" t="n">
-        <v>74.19067400993146</v>
+        <v>60.83890523217485</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.04572553593887</v>
+        <v>11.00146477378976</v>
       </c>
       <c r="C4" t="n">
-        <v>74.7512519490564</v>
+        <v>80.20093345533043</v>
       </c>
       <c r="D4" t="n">
-        <v>107.7045953898048</v>
+        <v>96.99667317958487</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.2252464970958</v>
+        <v>19.09499284760047</v>
       </c>
       <c r="C5" t="n">
-        <v>87.54735152620933</v>
+        <v>183.9795197758523</v>
       </c>
       <c r="D5" t="n">
-        <v>65.89981464756715</v>
+        <v>76.99356370555611</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.40508625342222</v>
+        <v>16.02015903789946</v>
       </c>
       <c r="C6" t="n">
-        <v>121.3587424604695</v>
+        <v>265.6206771133128</v>
       </c>
       <c r="D6" t="n">
-        <v>31.43654323768712</v>
+        <v>46.65166915810419</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>118.0365082292982</v>
+        <v>164.3887443376071</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>84.61683462903258</v>
+        <v>59.83261383532185</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.35381438862312</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.585342615909352</v>
+        <v>0.430005494460103</v>
       </c>
       <c r="C2" t="n">
-        <v>5.730461349688632</v>
+        <v>2.768528525976005</v>
       </c>
       <c r="D2" t="n">
-        <v>12.87071240267568</v>
+        <v>10.58127675637212</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50870954171587</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="C3" t="n">
-        <v>58.55143308127977</v>
+        <v>24.1166323548229</v>
       </c>
       <c r="D3" t="n">
-        <v>71.66758241001716</v>
+        <v>59.40555358397449</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.57573042751191</v>
+        <v>8.819039627249097</v>
       </c>
       <c r="C4" t="n">
-        <v>113.9200401053914</v>
+        <v>70.39916437613027</v>
       </c>
       <c r="D4" t="n">
-        <v>119.5739251341488</v>
+        <v>105.3052040006256</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.29320807286709</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1218792218388</v>
+        <v>174.9228972041755</v>
       </c>
       <c r="D5" t="n">
-        <v>82.78587516061229</v>
+        <v>89.04451677518571</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>19.15978819608075</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2455637370406</v>
+        <v>289.3691540790432</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>55.82904669740338</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>145.5244622005047</v>
+        <v>243.4390694835603</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>110.3189895262141</v>
+        <v>100.7224057172015</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>55.1359328182051</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.579452129683871</v>
+        <v>0.6842781498600269</v>
       </c>
       <c r="C2" t="n">
-        <v>7.241371066524473</v>
+        <v>14.6957813848705</v>
       </c>
       <c r="D2" t="n">
-        <v>15.32115467247572</v>
+        <v>11.8202423591316</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>2.105848825609408</v>
       </c>
       <c r="C3" t="n">
-        <v>39.46134897220054</v>
+        <v>17.11186248502191</v>
       </c>
       <c r="D3" t="n">
-        <v>65.85563600087605</v>
+        <v>54.52626749386786</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.47661496711199</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C4" t="n">
-        <v>130.3073727846792</v>
+        <v>65.23026271327082</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8231501823072</v>
+        <v>110.1167494991392</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.74190783143688</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C5" t="n">
-        <v>160.589380722172</v>
+        <v>154.7234381892973</v>
       </c>
       <c r="D5" t="n">
-        <v>102.8626157124596</v>
+        <v>103.7461886462817</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>157.9072459941697</v>
+        <v>285.5452467710019</v>
       </c>
       <c r="D6" t="n">
-        <v>52.68941753922207</v>
+        <v>68.06555008313562</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>170.8564982131851</v>
+        <v>324.5255393681214</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>148.4549790976814</v>
+        <v>195.1027212649686</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>89.63749238855074</v>
+        <v>78.32186834940201</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.112721059539136</v>
+        <v>0.4643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>3.418445506187394</v>
+        <v>7.759733854366789</v>
       </c>
       <c r="D2" t="n">
-        <v>10.68534201302228</v>
+        <v>8.60600037542754</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>2.969786805346601</v>
       </c>
       <c r="C3" t="n">
-        <v>37.16405934426301</v>
+        <v>33.78193850313274</v>
       </c>
       <c r="D3" t="n">
-        <v>65.49729808882596</v>
+        <v>58.62997289761952</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.7949222074662</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0603732738365</v>
+        <v>91.0747710275681</v>
       </c>
       <c r="D4" t="n">
-        <v>133.3959510622396</v>
+        <v>112.3374628061455</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.7054032399305</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>205.0380080319464</v>
+        <v>236.6011967234813</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2376843932109</v>
+        <v>96.60397409788617</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.14849024971531</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="C6" t="n">
-        <v>195.2205309894783</v>
+        <v>280.9163063454781</v>
       </c>
       <c r="D6" t="n">
-        <v>51.64287448649497</v>
+        <v>59.00892751145879</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>184.2112122340545</v>
+        <v>137.200223416196</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>111.1534750748239</v>
+        <v>57.66295140893641</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.288453898599315</v>
+        <v>0.2061670178918302</v>
       </c>
       <c r="C2" t="n">
-        <v>5.008876787067226</v>
+        <v>3.565707661824415</v>
       </c>
       <c r="D2" t="n">
-        <v>14.28737433990383</v>
+        <v>6.274349577841365</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.96750451476862</v>
+        <v>2.292380889416302</v>
       </c>
       <c r="C3" t="n">
-        <v>25.02965771977243</v>
+        <v>31.92152660358504</v>
       </c>
       <c r="D3" t="n">
-        <v>60.0829594999048</v>
+        <v>52.17989048071797</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.51039529968388</v>
+        <v>8.19366633964388</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3840058588726</v>
+        <v>84.83380087167113</v>
       </c>
       <c r="D4" t="n">
-        <v>135.0040538017959</v>
+        <v>110.9973771898486</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.77398671050754</v>
+        <v>12.4681958439345</v>
       </c>
       <c r="C5" t="n">
-        <v>223.4948648717864</v>
+        <v>182.8014225307561</v>
       </c>
       <c r="D5" t="n">
-        <v>126.277298458746</v>
+        <v>102.5680914011855</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.48058301565798</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>253.5854320069512</v>
+        <v>270.5313791299554</v>
       </c>
       <c r="D6" t="n">
-        <v>67.86429180376503</v>
+        <v>61.50453017565419</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>227.5691178444106</v>
+        <v>182.3547273253238</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>167.1474553865407</v>
+        <v>69.01195487002953</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>21.07812321017901</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.606139244147782</v>
+        <v>0.4977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>2.959969328304133</v>
+        <v>12.64981916922015</v>
       </c>
       <c r="D2" t="n">
-        <v>11.30384306669777</v>
+        <v>7.163812997888975</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.33780332571891</v>
+        <v>1.428442909679109</v>
       </c>
       <c r="C3" t="n">
-        <v>22.75200304591983</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="D3" t="n">
-        <v>58.75269136065037</v>
+        <v>45.34201772063894</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.88578277560466</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C4" t="n">
-        <v>94.80148531288899</v>
+        <v>82.05152787783568</v>
       </c>
       <c r="D4" t="n">
-        <v>134.8381384397782</v>
+        <v>112.120496563507</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.65189014228245</v>
+        <v>12.56637061435918</v>
       </c>
       <c r="C5" t="n">
-        <v>225.4829039728862</v>
+        <v>170.3577703794278</v>
       </c>
       <c r="D5" t="n">
-        <v>137.7146592132214</v>
+        <v>118.5951226730147</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>297.9427567802306</v>
+        <v>282.2043593334499</v>
       </c>
       <c r="D6" t="n">
-        <v>81.06683493047613</v>
+        <v>78.0479607399172</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33097214951819</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>278.2930764797306</v>
+        <v>291.8873369404362</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>206.4517247260617</v>
+        <v>154.8805178219768</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>80.76249314215958</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.85312305945724</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.475967710110456</v>
+        <v>0.5546874528994479</v>
       </c>
       <c r="C2" t="n">
-        <v>9.122399667861362</v>
+        <v>17.9591107537869</v>
       </c>
       <c r="D2" t="n">
-        <v>14.47292465600648</v>
+        <v>8.642325040484671</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.035604959260143</v>
+        <v>1.546252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>17.65673246087889</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D3" t="n">
-        <v>54.72261703471722</v>
+        <v>40.85052197370978</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.64030479181395</v>
+        <v>4.518002934943822</v>
       </c>
       <c r="C4" t="n">
-        <v>77.20169421885643</v>
+        <v>67.20848433732814</v>
       </c>
       <c r="D4" t="n">
-        <v>133.3193747413084</v>
+        <v>109.7083424541726</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.35107443415542</v>
+        <v>11.19192382841364</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3690369347268</v>
+        <v>160.7611865704152</v>
       </c>
       <c r="D5" t="n">
-        <v>149.8637870532756</v>
+        <v>130.8178815908875</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.05168244208915</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="C6" t="n">
-        <v>325.9176576127434</v>
+        <v>275.2810745231014</v>
       </c>
       <c r="D6" t="n">
-        <v>98.09328536522857</v>
+        <v>94.10837143369076</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>338.0000266089088</v>
+        <v>350.6959879202286</v>
       </c>
       <c r="D7" t="n">
-        <v>52.81998998388688</v>
+        <v>53.71828913327272</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>268.53744954263</v>
+        <v>265.8670957870787</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>144.1078002632765</v>
+        <v>119.479677354541</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>54.37900533823083</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.499349728563132</v>
+        <v>3.07188856658827</v>
       </c>
       <c r="C2" t="n">
-        <v>9.462084373530759</v>
+        <v>4.430627389265855</v>
       </c>
       <c r="D2" t="n">
-        <v>9.710466542705202</v>
+        <v>9.585784584265856</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.789726064841935</v>
+        <v>0.3063052837250048</v>
       </c>
       <c r="C2" t="n">
-        <v>5.254313713128929</v>
+        <v>22.1933886022034</v>
       </c>
       <c r="D2" t="n">
-        <v>10.76780882017902</v>
+        <v>15.84148095572653</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.02502671869168</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C3" t="n">
-        <v>25.4714441866835</v>
+        <v>51.80191761458295</v>
       </c>
       <c r="D3" t="n">
-        <v>60.02896337617122</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.30993884156828</v>
+        <v>3.75223972563131</v>
       </c>
       <c r="C4" t="n">
-        <v>112.0183948022653</v>
+        <v>77.03577885683872</v>
       </c>
       <c r="D4" t="n">
-        <v>137.7225131948553</v>
+        <v>105.8284755269892</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.77779052813751</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="C5" t="n">
-        <v>288.5356502781376</v>
+        <v>143.8014949795516</v>
       </c>
       <c r="D5" t="n">
-        <v>137.1992416684918</v>
+        <v>137.1256105906733</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.22770871412303</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>283.2911540420512</v>
+        <v>265.2986638663199</v>
       </c>
       <c r="D6" t="n">
-        <v>78.32972233103602</v>
+        <v>110.1687821274643</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C7" t="n">
-        <v>188.8224812009018</v>
+        <v>374.7704051237689</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>64.43799231594365</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>350.4839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>208.7843572713521</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>84.13086951543042</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.015168183920207</v>
+        <v>2.904009709162065</v>
       </c>
       <c r="C2" t="n">
-        <v>8.44597549963531</v>
+        <v>11.2037048008646</v>
       </c>
       <c r="D2" t="n">
-        <v>13.75330358879357</v>
+        <v>16.16643944583222</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.562222639363933</v>
+        <v>5.085453107998478</v>
       </c>
       <c r="C3" t="n">
-        <v>23.84174299763379</v>
+        <v>8.74737204483908</v>
       </c>
       <c r="D3" t="n">
-        <v>11.29500733735955</v>
+        <v>9.576948854927634</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39793808950696</v>
+        <v>11.67873072571836</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14214646859524</v>
+        <v>59.95081772535423</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57622801053023</v>
+        <v>0.7785820483812238</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.206788912697583</v>
+        <v>2.504438393533613</v>
       </c>
       <c r="C2" t="n">
-        <v>5.799183688985909</v>
+        <v>6.932120539686728</v>
       </c>
       <c r="D2" t="n">
-        <v>22.47711368873073</v>
+        <v>14.7753029489145</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26265072084841</v>
+        <v>8.261406931236911</v>
       </c>
       <c r="C3" t="n">
-        <v>29.53097094374406</v>
+        <v>32.06388002070083</v>
       </c>
       <c r="D3" t="n">
-        <v>20.11601046001715</v>
+        <v>21.39719121405923</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.23119373658351</v>
+        <v>6.457936398535519</v>
       </c>
       <c r="C4" t="n">
-        <v>36.88426124855267</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="D4" t="n">
-        <v>20.99467465531804</v>
+        <v>19.24618199405447</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44030009547687</v>
+        <v>13.63177869971702</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14062158529204</v>
+        <v>73.7719788455274</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250589493784605</v>
+        <v>1.603738670554944</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.026548245743669</v>
+        <v>2.465168485363741</v>
       </c>
       <c r="C2" t="n">
-        <v>7.596763735461819</v>
+        <v>10.7589730908408</v>
       </c>
       <c r="D2" t="n">
-        <v>30.74146586308037</v>
+        <v>11.79766216193392</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.31035544772901</v>
+        <v>8.585383673638358</v>
       </c>
       <c r="C3" t="n">
-        <v>25.30945581548277</v>
+        <v>28.85356502781376</v>
       </c>
       <c r="D3" t="n">
-        <v>33.4285093296039</v>
+        <v>28.63758053287946</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.71764187627119</v>
+        <v>12.20116046837936</v>
       </c>
       <c r="C4" t="n">
-        <v>58.70851271395926</v>
+        <v>55.95176516043422</v>
       </c>
       <c r="D4" t="n">
-        <v>26.35501712050563</v>
+        <v>25.80622015383166</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.16108873895449</v>
+        <v>6.528622233241291</v>
       </c>
       <c r="C5" t="n">
-        <v>41.13522880794136</v>
+        <v>18.62866268808323</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>27.02260555939346</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73138997457471</v>
+        <v>14.84642954016963</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0614788449057</v>
+        <v>87.42897395877672</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182847493643678</v>
+        <v>2.474404923361605</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.14926670877452</v>
+        <v>1.657190124768616</v>
       </c>
       <c r="C2" t="n">
-        <v>4.294164458375548</v>
+        <v>9.288315029879072</v>
       </c>
       <c r="D2" t="n">
-        <v>26.67801211520282</v>
+        <v>16.04273923509713</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29210315197582</v>
+        <v>8.585383673638358</v>
       </c>
       <c r="C3" t="n">
-        <v>27.95035713990669</v>
+        <v>36.89898746411637</v>
       </c>
       <c r="D3" t="n">
-        <v>49.35736583100839</v>
+        <v>31.43065275146164</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.24015263910875</v>
+        <v>14.90685714128357</v>
       </c>
       <c r="C4" t="n">
-        <v>60.66120889770617</v>
+        <v>65.76629695978959</v>
       </c>
       <c r="D4" t="n">
-        <v>36.59071868498287</v>
+        <v>34.11475097487241</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.08932334555324</v>
+        <v>12.78726384781471</v>
       </c>
       <c r="C5" t="n">
-        <v>77.45989386507335</v>
+        <v>67.76513528563609</v>
       </c>
       <c r="D5" t="n">
-        <v>32.5203927031756</v>
+        <v>30.53235360207581</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781152377410974</v>
+        <v>6.883033154474389</v>
       </c>
       <c r="C6" t="n">
-        <v>39.52712606838509</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05123382257515</v>
+        <v>16.09533124098296</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7628111282283</v>
+        <v>101.6547236272608</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017077940858382</v>
+        <v>3.388490787575361</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.960771149559132</v>
+        <v>1.213440162449058</v>
       </c>
       <c r="C2" t="n">
-        <v>6.455972903127026</v>
+        <v>7.10098114481718</v>
       </c>
       <c r="D2" t="n">
-        <v>20.7148765596077</v>
+        <v>21.72902193809465</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17291076913446</v>
+        <v>7.053857255013333</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2534551386117</v>
+        <v>36.40811361199297</v>
       </c>
       <c r="D3" t="n">
-        <v>55.18403845571321</v>
+        <v>36.62900684544849</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.27545449873262</v>
+        <v>15.78748483199296</v>
       </c>
       <c r="C4" t="n">
-        <v>54.48405234258524</v>
+        <v>80.90288306386691</v>
       </c>
       <c r="D4" t="n">
-        <v>45.57567367424968</v>
+        <v>41.4277896238069</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.70229376590174</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>71.34851440613696</v>
+        <v>97.34028487607128</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>35.9810533606456</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>55.4667817945363</v>
+        <v>66.65674212754145</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>36.18623863083319</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>25.27214940272139</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052540542228805</v>
+        <v>17.37072473295752</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11756758339504</v>
+        <v>115.5153194741675</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407837838893003</v>
+        <v>4.342681183239379</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.293583621298801</v>
+        <v>1.164352777236717</v>
       </c>
       <c r="C2" t="n">
-        <v>3.981968688425063</v>
+        <v>6.81136557206437</v>
       </c>
       <c r="D2" t="n">
-        <v>23.40290177383547</v>
+        <v>29.41414296693868</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52281386247382</v>
+        <v>5.48796966673967</v>
       </c>
       <c r="C3" t="n">
-        <v>23.45886139297754</v>
+        <v>31.76444697090555</v>
       </c>
       <c r="D3" t="n">
-        <v>59.248473951295</v>
+        <v>44.47807974090175</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.35501712050563</v>
+        <v>14.68989089864502</v>
       </c>
       <c r="C4" t="n">
-        <v>52.23781359526853</v>
+        <v>85.43364871896593</v>
       </c>
       <c r="D4" t="n">
-        <v>63.48177005200726</v>
+        <v>49.05989627662161</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.5808190924824</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>89.43721585688444</v>
+        <v>124.3874341280709</v>
       </c>
       <c r="D5" t="n">
-        <v>41.13522880794136</v>
+        <v>42.43604451606839</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.07928488433252</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>89.64043763166353</v>
+        <v>110.5712986862055</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>57.19171251089794</v>
+        <v>59.22785724950582</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>27.28767743954009</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.273026995915334</v>
+        <v>18.66543294783293</v>
       </c>
       <c r="C21" t="n">
-        <v>75.4576550826216</v>
+        <v>128.8803703540845</v>
       </c>
       <c r="D21" t="n">
-        <v>5.4547702469365</v>
+        <v>5.332980842237979</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.849432748351743</v>
+        <v>1.108393158094649</v>
       </c>
       <c r="C2" t="n">
-        <v>4.57985304031137</v>
+        <v>4.19500794024662</v>
       </c>
       <c r="D2" t="n">
-        <v>23.92420980479052</v>
+        <v>22.99547647657304</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.55364895193297</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85446466005999</v>
+        <v>47.48222771589698</v>
       </c>
       <c r="D3" t="n">
-        <v>64.2210260733051</v>
+        <v>50.62382036948678</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>9.929396280752242</v>
       </c>
       <c r="C4" t="n">
-        <v>55.51783267515713</v>
+        <v>116.2173297333289</v>
       </c>
       <c r="D4" t="n">
-        <v>78.93742415996479</v>
+        <v>48.05164138436013</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>10.16108873895449</v>
       </c>
       <c r="C5" t="n">
-        <v>93.5850999073272</v>
+        <v>66.07162049581035</v>
       </c>
       <c r="D5" t="n">
-        <v>54.24156065963628</v>
+        <v>36.1528592088888</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>6.762278186852032</v>
       </c>
       <c r="C6" t="n">
-        <v>118.7021331727776</v>
+        <v>39.00385454202154</v>
       </c>
       <c r="D6" t="n">
-        <v>39.84913931537804</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>96.11800898428396</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>53.90776644019235</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.480973076091251</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.16094710602658</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.545851441579845</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
